--- a/etf_holdings/2026-10-22_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-22_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,52 +486,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>3.89%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3.60%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
       <c r="J2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>2416000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2117000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-299,000</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-21_00981A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,55 +564,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>8348000</v>
+        <v>1474000</v>
       </c>
       <c r="K3" t="n">
-        <v>8895000</v>
+        <v>2005000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>547,000</t>
+          <t>531,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-21_00981A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -609,55 +627,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2235000</v>
+        <v>1616000</v>
       </c>
       <c r="K4" t="n">
-        <v>2275000</v>
+        <v>2170000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>554,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-21_00403A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -667,60 +685,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.90%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.17%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7000000</v>
+        <v>485000</v>
       </c>
       <c r="K5" t="n">
-        <v>7200000</v>
+        <v>320000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>-165,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-21_00403A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -735,55 +753,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1115000</v>
+        <v>2293000</v>
       </c>
       <c r="K6" t="n">
-        <v>1000000</v>
+        <v>1935000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-115,000</t>
+          <t>-358,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-21_00403A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -793,915 +811,1257 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10000</v>
+        <v>142000</v>
       </c>
       <c r="K7" t="n">
-        <v>10217</v>
+        <v>100000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-42,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-21_00405A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>148000</v>
+      </c>
       <c r="K8" t="n">
-        <v>379000</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>110000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-38,000</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.88%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>+0.49%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>484000</v>
+      </c>
       <c r="K9" t="n">
-        <v>52000</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>747000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>263,000</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.41%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+0.43%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>718000</v>
+      </c>
       <c r="K10" t="n">
-        <v>251000</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>966000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>248,000</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>聯強</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.51%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>3.81%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.65%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>166000</v>
+      </c>
       <c r="K11" t="n">
-        <v>1456000</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>144000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-22,000</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>+0.49%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2962622</v>
+      </c>
       <c r="K12" t="n">
-        <v>186000</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>4850622</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1,888,000</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6147</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>頎邦</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.08%</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>+0.47%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2781000</v>
+      </c>
       <c r="K13" t="n">
-        <v>174000</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>3904000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1,123,000</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6196</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.93%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>38000</v>
+      </c>
       <c r="K14" t="n">
-        <v>145000</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>56000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.64%</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>+0.53%</t>
+        </is>
+      </c>
       <c r="J15" t="n">
-        <v>227000</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+        <v>195000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>364000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>169,000</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
       <c r="J16" t="n">
-        <v>42000</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+        <v>161600</v>
+      </c>
+      <c r="K16" t="n">
+        <v>119600</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-42,000</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>志聖</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>+0.49%</t>
+        </is>
+      </c>
       <c r="J17" t="n">
-        <v>98000</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <v>948000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1411000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>463,000</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>鈊象</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.26%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
       <c r="J18" t="n">
-        <v>159000</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+        <v>204000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-94,000</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>裕民</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.41%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>2.49%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
       <c r="J19" t="n">
-        <v>526000</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+        <v>59000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>45000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-14,000</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>晶技</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
-        <v>310000</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+        <v>44000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-32,000</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.59%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.64%</t>
+        </is>
+      </c>
       <c r="J21" t="n">
-        <v>219000</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+        <v>104000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-14,000</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>世界</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.31%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
       <c r="J22" t="n">
-        <v>177000</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+        <v>48336</v>
+      </c>
+      <c r="K22" t="n">
+        <v>110336</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>62,000</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>寶雅*</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>寶雅*</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.79%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+        <v>2255500</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2060500</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-195,000</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.02%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1.40%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>396000</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+        <v>143000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>176000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>33,000</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>同欣電</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>114000</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+        <v>155105</v>
+      </c>
+      <c r="K25" t="n">
+        <v>185105</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>尖點</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>邁科</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>邁科</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.97%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>183000</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+        <v>182000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>129000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-53,000</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1711,60 +2071,60 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>846000</v>
+        <v>103000</v>
       </c>
       <c r="K27" t="n">
-        <v>1399000</v>
+        <v>87000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>553,000</t>
+          <t>-16,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1774,60 +2134,60 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>178000</v>
+        <v>168000</v>
       </c>
       <c r="K28" t="n">
-        <v>210000</v>
+        <v>104000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>-64,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1842,55 +2202,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>829000</v>
+        <v>851000</v>
       </c>
       <c r="K29" t="n">
-        <v>856000</v>
+        <v>951000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1900,60 +2260,60 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>10000</v>
+        <v>2199000</v>
       </c>
       <c r="K30" t="n">
-        <v>23000</v>
+        <v>1299000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>-900,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1963,60 +2323,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1333000</v>
+        <v>1640000</v>
       </c>
       <c r="K31" t="n">
-        <v>1753000</v>
+        <v>990000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>420,000</t>
+          <t>-650,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2031,55 +2391,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>189000</v>
+        <v>3638000</v>
       </c>
       <c r="K32" t="n">
-        <v>241000</v>
+        <v>4838000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2094,48 +2454,48 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8.66%</t>
+          <t>3.64%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8.58%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>333000</v>
+        <v>2110000</v>
       </c>
       <c r="K33" t="n">
-        <v>342000</v>
+        <v>2290000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+          <t>2026-10-21_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2147,55 +2507,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1.48%</t>
-        </is>
-      </c>
+          <t>東和鋼鐵</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-1.21%</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>896000</v>
-      </c>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
-        <v>165000</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>-731,000</t>
-        </is>
-      </c>
+        <v>379000</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2210,55 +2552,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1.19%</t>
-        </is>
-      </c>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.62%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>-0.57%</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>56000</v>
-      </c>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
-        <v>33000</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>-23,000</t>
-        </is>
-      </c>
+        <v>52000</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2273,55 +2597,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.33%</t>
-        </is>
-      </c>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.25%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>+0.92%</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>26000</v>
-      </c>
+          <t>1.41%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
-        <v>101000</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>75,000</t>
-        </is>
-      </c>
+        <v>251000</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2336,55 +2642,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6.05%</t>
-        </is>
-      </c>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.82%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-1.23%</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>113000</v>
-      </c>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>93000</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>-20,000</t>
-        </is>
-      </c>
+        <v>1456000</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2399,55 +2687,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1.52%</t>
-        </is>
-      </c>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-0.60%</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>206000</v>
-      </c>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>130000</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>-76,000</t>
-        </is>
-      </c>
+        <v>186000</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2462,55 +2732,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2.64%</t>
-        </is>
-      </c>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.65%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-0.99%</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>577000</v>
-      </c>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
-        <v>363000</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-214,000</t>
-        </is>
-      </c>
+        <v>174000</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2525,55 +2777,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.48%</t>
-        </is>
-      </c>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2.97%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>+1.49%</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>33000</v>
-      </c>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
-        <v>69000</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>36,000</t>
-        </is>
-      </c>
+        <v>145000</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2588,55 +2822,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.81%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>1.23%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>+0.42%</t>
-        </is>
-      </c>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>154000</v>
-      </c>
-      <c r="K41" t="n">
-        <v>242000</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>88,000</t>
-        </is>
-      </c>
+        <v>227000</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2651,55 +2867,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.62%</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.83%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-0.79%</t>
-        </is>
-      </c>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>25000</v>
-      </c>
-      <c r="K42" t="n">
-        <v>13000</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>-12,000</t>
-        </is>
-      </c>
+        <v>42000</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2714,55 +2912,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.33%</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-2.30%</t>
-        </is>
-      </c>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>176000</v>
-      </c>
-      <c r="K43" t="n">
-        <v>120000</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-56,000</t>
-        </is>
-      </c>
+        <v>98000</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2777,55 +2957,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6.01%</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>4.95%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-1.06%</t>
-        </is>
-      </c>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>526000</v>
-      </c>
-      <c r="K44" t="n">
-        <v>433000</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-93,000</t>
-        </is>
-      </c>
+        <v>159000</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2840,55 +3002,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
+          <t>裕民</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.83%</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.38%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-0.45%</t>
-        </is>
-      </c>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>136000</v>
-      </c>
-      <c r="K45" t="n">
-        <v>62000</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-74,000</t>
-        </is>
-      </c>
+        <v>526000</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2903,55 +3047,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2.92%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>+1.60%</t>
-        </is>
-      </c>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>49000</v>
-      </c>
-      <c r="K46" t="n">
-        <v>107000</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>58,000</t>
-        </is>
-      </c>
+        <v>310000</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -2966,55 +3092,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4.75%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>5.64%</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>+0.89%</t>
-        </is>
-      </c>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>464000</v>
-      </c>
-      <c r="K47" t="n">
-        <v>538000</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>74,000</t>
-        </is>
-      </c>
+        <v>219000</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -3029,55 +3137,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.77%</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>5.90%</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>+2.13%</t>
-        </is>
-      </c>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>45000</v>
-      </c>
-      <c r="K48" t="n">
-        <v>71000</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
+        <v>177000</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -3092,55 +3182,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
+          <t>1.79%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K49" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-44,000</t>
-        </is>
-      </c>
+        <v>125000</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -3155,55 +3227,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1.56%</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>+0.77%</t>
-        </is>
-      </c>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>11000</v>
-      </c>
-      <c r="K50" t="n">
-        <v>23000</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
+        <v>396000</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -3218,55 +3272,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>0.61%</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>+0.32%</t>
-        </is>
-      </c>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>14000</v>
-      </c>
-      <c r="K51" t="n">
-        <v>30000</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>16,000</t>
-        </is>
-      </c>
+        <v>114000</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -3281,55 +3317,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
+          <t>尖點</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.80%</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>1.83%</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>252000</v>
-      </c>
-      <c r="K52" t="n">
-        <v>258000</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
+        <v>183000</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>2026-10-21_00993A_full_holdings.xlsx</t>
@@ -3349,48 +3367,48 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>427000</v>
+        <v>846000</v>
       </c>
       <c r="K53" t="n">
-        <v>328000</v>
+        <v>1399000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-99,000</t>
+          <t>553,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3417,43 +3435,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>25600</v>
+        <v>178000</v>
       </c>
       <c r="K54" t="n">
-        <v>27600</v>
+        <v>210000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3475,48 +3493,48 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>76000</v>
+        <v>829000</v>
       </c>
       <c r="K55" t="n">
-        <v>51000</v>
+        <v>856000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-25,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3538,48 +3556,48 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-2.11%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>249000</v>
+        <v>10000</v>
       </c>
       <c r="K56" t="n">
-        <v>133000</v>
+        <v>23000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-116,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3601,48 +3619,48 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1092000</v>
+        <v>1333000</v>
       </c>
       <c r="K57" t="n">
-        <v>478000</v>
+        <v>1753000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-614,000</t>
+          <t>420,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3664,48 +3682,48 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>99191</v>
+        <v>189000</v>
       </c>
       <c r="K58" t="n">
-        <v>55191</v>
+        <v>241000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-44,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3727,48 +3745,48 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>8.66%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>8.58%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>51000</v>
+        <v>333000</v>
       </c>
       <c r="K59" t="n">
-        <v>48000</v>
+        <v>342000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3795,43 +3813,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>281000</v>
+        <v>896000</v>
       </c>
       <c r="K60" t="n">
-        <v>205000</v>
+        <v>165000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-76,000</t>
+          <t>-731,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3858,43 +3876,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>100000</v>
+        <v>56000</v>
       </c>
       <c r="K61" t="n">
-        <v>44000</v>
+        <v>33000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-56,000</t>
+          <t>-23,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3906,196 +3924,1834 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>+0.92%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>26000</v>
+      </c>
       <c r="K62" t="n">
-        <v>245000</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
+        <v>101000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>75,000</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-10-21_00400A_full_holdings.xlsx</t>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>6.05%</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>4.82%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-1.23%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>113000</v>
+      </c>
       <c r="K63" t="n">
-        <v>279000</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
+        <v>93000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-10-21_00400A_full_holdings.xlsx</t>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.35%</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
       <c r="J64" t="n">
-        <v>221000</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+        <v>206000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>130000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-76,000</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-10-21_00400A_full_holdings.xlsx</t>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2.64%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>577000</v>
+      </c>
+      <c r="K65" t="n">
+        <v>363000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-214,000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2.97%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>+1.49%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>33000</v>
+      </c>
+      <c r="K66" t="n">
+        <v>69000</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>36,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>154000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>242000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>88,000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-12,000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>6.33%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-2.30%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>176000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-56,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-1.06%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>526000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>433000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-93,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>136000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>62000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-74,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2.92%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+1.60%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>107000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>58,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>5.64%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+0.89%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>464000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>538000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>74,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>3.77%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>5.90%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>+2.13%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>45000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>71000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-0.62%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>64000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-44,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>+0.77%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>11000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>23000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>14000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>252000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>258000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>427000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>328000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-99,000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>4.73%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>25600</v>
+      </c>
+      <c r="K80" t="n">
+        <v>27600</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>76000</v>
+      </c>
+      <c r="K81" t="n">
+        <v>51000</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-25,000</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>4.18%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-2.11%</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>249000</v>
+      </c>
+      <c r="K82" t="n">
+        <v>133000</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>-116,000</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-0.72%</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>1092000</v>
+      </c>
+      <c r="K83" t="n">
+        <v>478000</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-614,000</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1.08%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>99191</v>
+      </c>
+      <c r="K84" t="n">
+        <v>55191</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-44,000</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>51000</v>
+      </c>
+      <c r="K85" t="n">
+        <v>48000</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>3.97%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-1.12%</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>281000</v>
+      </c>
+      <c r="K86" t="n">
+        <v>205000</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-76,000</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-0.91%</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K87" t="n">
+        <v>44000</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-56,000</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-10-21_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>245000</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10-21_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>279000</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-10-21_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>221000</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-10-21_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>7769</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>鴻勁</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>鴻勁</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>0.12%</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>0.70%</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>+0.58%</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J91" t="n">
         <v>7000</v>
       </c>
-      <c r="K65" t="n">
+      <c r="K91" t="n">
         <v>40000</v>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>33,000</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>2026-10-21_00400A_full_holdings.xlsx</t>
         </is>
